--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_140_R14.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_140_R14.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4441</v>
+        <v>4.0334</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9739</v>
+        <v>4.161</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4702</v>
+        <v>-0.1277</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1942</v>
+        <v>4.4071</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6028</v>
+        <v>0.76</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7969</v>
+        <v>3.6471</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5803</v>
+        <v>5.9692</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1449</v>
+        <v>1.5293</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4354</v>
+        <v>4.44</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3861</v>
+        <v>-1.5621</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7477</v>
+        <v>-0.7692</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3615</v>
+        <v>-0.7929</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3041</v>
+        <v>-0.6959</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5534</v>
+        <v>-0.4165</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7508</v>
+        <v>-0.2794</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1418</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5616</v>
+        <v>3.65</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6892</v>
+        <v>2.7511</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1277</v>
+        <v>0.8988</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4071</v>
+        <v>1.1942</v>
       </c>
       <c r="H3" t="n">
-        <v>0.76</v>
+        <v>-0.6028</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6471</v>
+        <v>1.7969</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9692</v>
+        <v>1.5803</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5293</v>
+        <v>0.1449</v>
       </c>
       <c r="L3" t="n">
-        <v>4.44</v>
+        <v>1.4354</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5621</v>
+        <v>-0.3861</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7692</v>
+        <v>-0.7477</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7929</v>
+        <v>0.3615</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1677</v>
+        <v>0.51</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8883</v>
+        <v>0.3306</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2794</v>
+        <v>0.1795</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1418</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4477</v>
+        <v>2.095</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0518</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3959</v>
+        <v>1.4967</v>
       </c>
       <c r="G4" t="n">
         <v>1.9243</v>
@@ -766,13 +766,13 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7033</v>
+        <v>-0.056</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8804</v>
+        <v>-0.3339</v>
       </c>
       <c r="U4" t="n">
-        <v>0.177</v>
+        <v>0.2779</v>
       </c>
       <c r="V4" t="n">
         <v>-1.8608</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8085</v>
+        <v>1.4297</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0698</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F5" t="n">
         <v>0.7387</v>
@@ -844,10 +844,10 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4075</v>
+        <v>-0.7863</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2617</v>
+        <v>-0.6405</v>
       </c>
       <c r="U5" t="n">
         <v>-0.1458</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3551</v>
+        <v>0.0751</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5071</v>
+        <v>-0.2566</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8622</v>
+        <v>0.3317</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6042</v>
+        <v>-2.0034</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1189</v>
+        <v>-2.7395</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4852</v>
+        <v>0.7361</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2405</v>
+        <v>-2.0712</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5412</v>
+        <v>-2.3387</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6993</v>
+        <v>0.2676</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6364</v>
+        <v>0.0678</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4223</v>
+        <v>-0.4008</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.214</v>
+        <v>0.4685</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0315</v>
+        <v>-0.9937</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1098</v>
+        <v>-0.4716</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9216</v>
+        <v>-0.5221</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5361</v>
+        <v>2.1444</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5361</v>
+        <v>2.2862</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.42</v>
+        <v>-0.5581</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4492</v>
+        <v>0.0353</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0292</v>
+        <v>-0.5933</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0034</v>
+        <v>0.6042</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.7395</v>
+        <v>0.1189</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7361</v>
+        <v>0.4852</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.0712</v>
+        <v>1.2405</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.3387</v>
+        <v>0.5412</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2676</v>
+        <v>0.6993</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0678</v>
+        <v>-0.6364</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4008</v>
+        <v>-0.4223</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4685</v>
+        <v>-0.214</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4888</v>
+        <v>-1.2344</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6642</v>
+        <v>-0.5816</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8246</v>
+        <v>-0.6528</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1444</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2862</v>
+        <v>0.5361</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0669</v>
+        <v>-0.8578</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3985</v>
+        <v>-2.3238</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3316</v>
+        <v>1.466</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6337</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4332</v>
+        <v>-0.224</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5228</v>
+        <v>-0.4481</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0896</v>
+        <v>0.224</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. EDWARDS</t>
+          <t>A. PAJOLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5662</v>
+        <v>-1.668</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1085</v>
+        <v>-2.3175</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4577</v>
+        <v>0.6495</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1616</v>
+        <v>-0.1989</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9177</v>
+        <v>-1.437</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7561</v>
+        <v>1.2381</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6221</v>
+        <v>-0.9102</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9804</v>
+        <v>-1.5727</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6025</v>
+        <v>0.6625</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7837</v>
+        <v>0.7113</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9373</v>
+        <v>0.1357</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8464</v>
+        <v>0.5756</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0593</v>
+        <v>-0.0953</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2513</v>
+        <v>-0.2475</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3106</v>
+        <v>0.1522</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9107</v>
+        <v>-1.6844</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2654</v>
+        <v>-2.0728</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3548</v>
+        <v>0.3884</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2372</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6734</v>
+        <v>-0.4472</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4402</v>
+        <v>-0.2475</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2333</v>
+        <v>-0.1997</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. PAJOLA</t>
+          <t>C. EDWARDS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0959</v>
+        <v>-1.8447</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5101</v>
+        <v>-1.1517</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4143</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1989</v>
+        <v>-1.1616</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.437</v>
+        <v>-1.9177</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2381</v>
+        <v>0.7561</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9102</v>
+        <v>0.6221</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5727</v>
+        <v>-0.9804</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6625</v>
+        <v>1.6025</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7113</v>
+        <v>-1.7837</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1357</v>
+        <v>-0.9373</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5756</v>
+        <v>-0.8464</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5232</v>
+        <v>-0.2192</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4402</v>
+        <v>-0.2946</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.083</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6849</v>
+        <v>-2.7611</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6937</v>
+        <v>-2.5011</v>
       </c>
       <c r="F13" t="n">
-        <v>0.008800000000000001</v>
+        <v>-0.26</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1057</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0457</v>
+        <v>-0.1219</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6721</v>
+        <v>-0.4795</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6264</v>
+        <v>0.3576</v>
       </c>
       <c r="V13" t="n">
         <v>0.3943</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4687999999999977</v>
+        <v>1.215700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.1336</v>
+        <v>-2.3868</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6025</v>
+        <v>3.602399999999999</v>
       </c>
       <c r="G14" t="n">
         <v>2.840500000000001</v>
@@ -1534,7 +1534,7 @@
         <v>-3.3295</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.621699999999999</v>
+        <v>-1.6217</v>
       </c>
       <c r="P14" t="n">
         <v>3.4793</v>
@@ -1546,13 +1546,13 @@
         <v>15.077</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.4254</v>
+        <v>-4.6784</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.5776</v>
+        <v>-3.830699999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8477999999999998</v>
+        <v>-0.8478000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-0.4253999999999994</v>
@@ -1561,7 +1561,7 @@
         <v>5.250300000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.675700000000001</v>
+        <v>-5.6757</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.297</v>
+        <v>6.257</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0679</v>
+        <v>4.4781</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2291</v>
+        <v>1.7789</v>
       </c>
       <c r="G15" t="n">
         <v>2.0957</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0416</v>
+        <v>1.0016</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8496</v>
+        <v>0.2598</v>
       </c>
       <c r="U15" t="n">
-        <v>0.192</v>
+        <v>0.7418</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>D. BERTANS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0341</v>
+        <v>2.1226</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9931</v>
+        <v>0.3886</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.959</v>
+        <v>1.734</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0211</v>
+        <v>0.8081</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7705</v>
+        <v>1.0758</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7494</v>
+        <v>-0.2677</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8011</v>
+        <v>1.1117</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6539</v>
+        <v>0.2185</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1472</v>
+        <v>0.8932</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.78</v>
+        <v>-0.3036</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8834</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8966</v>
+        <v>-1.1609</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6419</v>
+        <v>1.8506</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3724</v>
+        <v>0.4367</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2696</v>
+        <v>1.4139</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7886</v>
+        <v>-0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8197</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.6083</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BERTANS</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1993</v>
+        <v>1.9904</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0832</v>
+        <v>3.2854</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2825</v>
+        <v>-1.295</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8081</v>
+        <v>0.0211</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0758</v>
+        <v>0.7705</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2677</v>
+        <v>-0.7494</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1117</v>
+        <v>1.8011</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2185</v>
+        <v>1.6539</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8932</v>
+        <v>0.1472</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3036</v>
+        <v>-1.78</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8574000000000001</v>
+        <v>-0.8834</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1609</v>
+        <v>-0.8966</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9272</v>
+        <v>1.5982</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0351</v>
+        <v>0.6647</v>
       </c>
       <c r="U17" t="n">
-        <v>1.9624</v>
+        <v>0.9335</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5361</v>
+        <v>-0.7886</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2605</v>
+        <v>1.0469</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6328</v>
+        <v>-0.161</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8934</v>
+        <v>1.2079</v>
       </c>
       <c r="G18" t="n">
         <v>1.2246</v>
@@ -1858,13 +1858,13 @@
         <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3224</v>
+        <v>0.4639</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8646</v>
+        <v>-0.3927</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5421</v>
+        <v>0.8566</v>
       </c>
       <c r="V18" t="n">
         <v>1.214</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1339</v>
+        <v>-0.5948</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8492</v>
+        <v>-2.3774</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7154</v>
+        <v>1.7826</v>
       </c>
       <c r="G19" t="n">
         <v>-2.9467</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5087</v>
+        <v>1.0477</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0316</v>
+        <v>0.5034</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4771</v>
+        <v>0.5443</v>
       </c>
       <c r="V19" t="n">
         <v>1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5492</v>
+        <v>-0.9376</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0396</v>
+        <v>-0.2558</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.6817</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3446</v>
+        <v>0.0747</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3685</v>
+        <v>-0.6481</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7131</v>
+        <v>0.7228</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0806</v>
+        <v>0.8683</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7933</v>
+        <v>-0.383</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7127</v>
+        <v>1.2514</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4252</v>
+        <v>-0.7937</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5752</v>
+        <v>-0.2651</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0004</v>
+        <v>-0.5286</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4037</v>
+        <v>0.5239</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0395</v>
+        <v>0.0356</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3642</v>
+        <v>0.4883</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6103</v>
+        <v>-1.9303</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4917</v>
+        <v>-1.2755</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1186</v>
+        <v>-0.6548</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0747</v>
+        <v>-0.3446</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6481</v>
+        <v>1.3685</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7228</v>
+        <v>-1.7131</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8683</v>
+        <v>0.0806</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.383</v>
+        <v>0.7933</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2514</v>
+        <v>-0.7127</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7937</v>
+        <v>-0.4252</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2651</v>
+        <v>0.5752</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5286</v>
+        <v>-1.0004</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1489</v>
+        <v>0.0226</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2003</v>
+        <v>-0.1964</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0514</v>
+        <v>0.219</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4882</v>
+        <v>-2.6632</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3073</v>
+        <v>-3.133</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1809</v>
+        <v>0.4697</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1075</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4955</v>
+        <v>0.3205</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6923</v>
+        <v>-0.1333</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1968</v>
+        <v>0.4538</v>
       </c>
       <c r="V22" t="n">
         <v>0.2836</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4781</v>
+        <v>-4.187</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2595</v>
+        <v>-4.5518</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2187</v>
+        <v>0.3647</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6656</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.122</v>
+        <v>0.1691</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0376</v>
+        <v>-0.3299</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0843</v>
+        <v>0.4991</v>
       </c>
       <c r="V23" t="n">
         <v>0.7886</v>
@@ -2281,25 +2281,25 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4688000000000008</v>
+        <v>1.104</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.602300000000001</v>
+        <v>-3.602399999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>3.1336</v>
+        <v>4.7063</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8402</v>
       </c>
       <c r="H24" t="n">
-        <v>6.344699999999999</v>
+        <v>6.3447</v>
       </c>
       <c r="I24" t="n">
-        <v>-9.184800000000001</v>
+        <v>-9.184799999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>4.951000000000001</v>
+        <v>4.951</v>
       </c>
       <c r="K24" t="n">
         <v>3.3293</v>
@@ -2326,13 +2326,13 @@
         <v>11.5979</v>
       </c>
       <c r="S24" t="n">
-        <v>5.425300000000001</v>
+        <v>6.9981</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8477999999999997</v>
+        <v>0.8478999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>4.5777</v>
+        <v>6.150300000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0.4254</v>
